--- a/data/dena_IME_mock_dataset_v2.xlsx
+++ b/data/dena_IME_mock_dataset_v2.xlsx
@@ -814,17 +814,14 @@
       <c r="D4" s="39" t="n">
         <v>320000</v>
       </c>
-      <c r="E4" s="39">
-        <f>'SOURCE 1 — SAP Finance'!G4</f>
-        <v/>
-      </c>
-      <c r="F4" s="40">
-        <f>E4/D4</f>
-        <v/>
-      </c>
-      <c r="G4" s="40">
-        <f>'SOURCE 3 — HR Timesheet'!E4/'SOURCE 3 — HR Timesheet'!D4</f>
-        <v/>
+      <c r="E4" s="39" t="n">
+        <v>285000</v>
+      </c>
+      <c r="F4" s="40" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="G4" s="40" t="n">
+        <v>0.66</v>
       </c>
       <c r="H4" s="37" t="inlineStr">
         <is>
@@ -871,17 +868,14 @@
       <c r="D5" s="45" t="n">
         <v>540000</v>
       </c>
-      <c r="E5" s="45">
-        <f>'SOURCE 1 — SAP Finance'!G5</f>
-        <v/>
-      </c>
-      <c r="F5" s="46">
-        <f>E5/D5</f>
-        <v/>
-      </c>
-      <c r="G5" s="46">
-        <f>'SOURCE 3 — HR Timesheet'!E5/'SOURCE 3 — HR Timesheet'!D5</f>
-        <v/>
+      <c r="E5" s="45" t="n">
+        <v>198000</v>
+      </c>
+      <c r="F5" s="46" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="G5" s="46" t="n">
+        <v>0.79</v>
       </c>
       <c r="H5" s="43" t="inlineStr">
         <is>
@@ -928,17 +922,14 @@
       <c r="D6" s="39" t="n">
         <v>210000</v>
       </c>
-      <c r="E6" s="39">
-        <f>'SOURCE 1 — SAP Finance'!G6</f>
-        <v/>
-      </c>
-      <c r="F6" s="40">
-        <f>E6/D6</f>
-        <v/>
-      </c>
-      <c r="G6" s="40">
-        <f>'SOURCE 3 — HR Timesheet'!E6/'SOURCE 3 — HR Timesheet'!D6</f>
-        <v/>
+      <c r="E6" s="39" t="n">
+        <v>204000</v>
+      </c>
+      <c r="F6" s="40" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="G6" s="40" t="n">
+        <v>0.61</v>
       </c>
       <c r="H6" s="37" t="inlineStr">
         <is>
@@ -985,17 +976,14 @@
       <c r="D7" s="45" t="n">
         <v>480000</v>
       </c>
-      <c r="E7" s="45">
-        <f>'SOURCE 1 — SAP Finance'!G7</f>
-        <v/>
-      </c>
-      <c r="F7" s="46">
-        <f>E7/D7</f>
-        <v/>
-      </c>
-      <c r="G7" s="46">
-        <f>'SOURCE 3 — HR Timesheet'!E7/'SOURCE 3 — HR Timesheet'!D7</f>
-        <v/>
+      <c r="E7" s="45" t="n">
+        <v>89000</v>
+      </c>
+      <c r="F7" s="46" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="G7" s="46" t="n">
+        <v>0.82</v>
       </c>
       <c r="H7" s="43" t="inlineStr">
         <is>
@@ -1042,17 +1030,14 @@
       <c r="D8" s="39" t="n">
         <v>95000</v>
       </c>
-      <c r="E8" s="39">
-        <f>'SOURCE 1 — SAP Finance'!G8</f>
-        <v/>
-      </c>
-      <c r="F8" s="40">
-        <f>E8/D8</f>
-        <v/>
-      </c>
-      <c r="G8" s="40">
-        <f>'SOURCE 3 — HR Timesheet'!E8/'SOURCE 3 — HR Timesheet'!D8</f>
-        <v/>
+      <c r="E8" s="39" t="n">
+        <v>91000</v>
+      </c>
+      <c r="F8" s="40" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G8" s="40" t="n">
+        <v>0.74</v>
       </c>
       <c r="H8" s="37" t="inlineStr">
         <is>
@@ -1099,17 +1084,14 @@
       <c r="D9" s="45" t="n">
         <v>275000</v>
       </c>
-      <c r="E9" s="45">
-        <f>'SOURCE 1 — SAP Finance'!G9</f>
-        <v/>
-      </c>
-      <c r="F9" s="46">
-        <f>E9/D9</f>
-        <v/>
-      </c>
-      <c r="G9" s="46">
-        <f>'SOURCE 3 — HR Timesheet'!E9/'SOURCE 3 — HR Timesheet'!D9</f>
-        <v/>
+      <c r="E9" s="45" t="n">
+        <v>132000</v>
+      </c>
+      <c r="F9" s="46" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="G9" s="46" t="n">
+        <v>0.75</v>
       </c>
       <c r="H9" s="43" t="inlineStr">
         <is>
@@ -1156,17 +1138,14 @@
       <c r="D10" s="39" t="n">
         <v>185000</v>
       </c>
-      <c r="E10" s="39">
-        <f>'SOURCE 1 — SAP Finance'!G10</f>
-        <v/>
-      </c>
-      <c r="F10" s="40">
-        <f>E10/D10</f>
-        <v/>
-      </c>
-      <c r="G10" s="40">
-        <f>'SOURCE 3 — HR Timesheet'!E10/'SOURCE 3 — HR Timesheet'!D10</f>
-        <v/>
+      <c r="E10" s="39" t="n">
+        <v>192000</v>
+      </c>
+      <c r="F10" s="40" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G10" s="40" t="n">
+        <v>0.91</v>
       </c>
       <c r="H10" s="37" t="inlineStr">
         <is>
@@ -1213,17 +1192,14 @@
       <c r="D11" s="45" t="n">
         <v>390000</v>
       </c>
-      <c r="E11" s="45">
-        <f>'SOURCE 1 — SAP Finance'!G11</f>
-        <v/>
-      </c>
-      <c r="F11" s="46">
-        <f>E11/D11</f>
-        <v/>
-      </c>
-      <c r="G11" s="46">
-        <f>'SOURCE 3 — HR Timesheet'!E11/'SOURCE 3 — HR Timesheet'!D11</f>
-        <v/>
+      <c r="E11" s="45" t="n">
+        <v>54000</v>
+      </c>
+      <c r="F11" s="46" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="G11" s="46" t="n">
+        <v>0.74</v>
       </c>
       <c r="H11" s="43" t="inlineStr">
         <is>
@@ -1270,17 +1246,14 @@
       <c r="D12" s="39" t="n">
         <v>620000</v>
       </c>
-      <c r="E12" s="39">
-        <f>'SOURCE 1 — SAP Finance'!G12</f>
-        <v/>
-      </c>
-      <c r="F12" s="40">
-        <f>E12/D12</f>
-        <v/>
-      </c>
-      <c r="G12" s="40">
-        <f>'SOURCE 3 — HR Timesheet'!E12/'SOURCE 3 — HR Timesheet'!D12</f>
-        <v/>
+      <c r="E12" s="39" t="n">
+        <v>178000</v>
+      </c>
+      <c r="F12" s="40" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="G12" s="40" t="n">
+        <v>0.66</v>
       </c>
       <c r="H12" s="37" t="inlineStr">
         <is>
@@ -1327,17 +1300,14 @@
       <c r="D13" s="45" t="n">
         <v>310000</v>
       </c>
-      <c r="E13" s="45">
-        <f>'SOURCE 1 — SAP Finance'!G13</f>
-        <v/>
-      </c>
-      <c r="F13" s="46">
-        <f>E13/D13</f>
-        <v/>
-      </c>
-      <c r="G13" s="46">
-        <f>'SOURCE 3 — HR Timesheet'!E13/'SOURCE 3 — HR Timesheet'!D13</f>
-        <v/>
+      <c r="E13" s="45" t="n">
+        <v>98000</v>
+      </c>
+      <c r="F13" s="46" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="G13" s="46" t="n">
+        <v>0.88</v>
       </c>
       <c r="H13" s="43" t="inlineStr">
         <is>
@@ -1384,17 +1354,14 @@
       <c r="D14" s="39" t="n">
         <v>145000</v>
       </c>
-      <c r="E14" s="39">
-        <f>'SOURCE 1 — SAP Finance'!G14</f>
-        <v/>
-      </c>
-      <c r="F14" s="40">
-        <f>E14/D14</f>
-        <v/>
-      </c>
-      <c r="G14" s="40">
-        <f>'SOURCE 3 — HR Timesheet'!E14/'SOURCE 3 — HR Timesheet'!D14</f>
-        <v/>
+      <c r="E14" s="39" t="n">
+        <v>138000</v>
+      </c>
+      <c r="F14" s="40" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G14" s="40" t="n">
+        <v>0.76</v>
       </c>
       <c r="H14" s="37" t="inlineStr">
         <is>
@@ -1441,17 +1408,14 @@
       <c r="D15" s="45" t="n">
         <v>260000</v>
       </c>
-      <c r="E15" s="45">
-        <f>'SOURCE 1 — SAP Finance'!G15</f>
-        <v/>
-      </c>
-      <c r="F15" s="46">
-        <f>E15/D15</f>
-        <v/>
-      </c>
-      <c r="G15" s="46">
-        <f>'SOURCE 3 — HR Timesheet'!E15/'SOURCE 3 — HR Timesheet'!D15</f>
-        <v/>
+      <c r="E15" s="45" t="n">
+        <v>72000</v>
+      </c>
+      <c r="F15" s="46" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="G15" s="46" t="n">
+        <v>0.65</v>
       </c>
       <c r="H15" s="43" t="inlineStr">
         <is>
@@ -1498,17 +1462,14 @@
       <c r="D16" s="39" t="n">
         <v>410000</v>
       </c>
-      <c r="E16" s="39">
-        <f>'SOURCE 1 — SAP Finance'!G16</f>
-        <v/>
-      </c>
-      <c r="F16" s="40">
-        <f>E16/D16</f>
-        <v/>
-      </c>
-      <c r="G16" s="40">
-        <f>'SOURCE 3 — HR Timesheet'!E16/'SOURCE 3 — HR Timesheet'!D16</f>
-        <v/>
+      <c r="E16" s="39" t="n">
+        <v>155000</v>
+      </c>
+      <c r="F16" s="40" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="G16" s="40" t="n">
+        <v>0.8100000000000001</v>
       </c>
       <c r="H16" s="37" t="inlineStr">
         <is>
@@ -1555,17 +1516,14 @@
       <c r="D17" s="45" t="n">
         <v>78000</v>
       </c>
-      <c r="E17" s="45">
-        <f>'SOURCE 1 — SAP Finance'!G17</f>
-        <v/>
-      </c>
-      <c r="F17" s="46">
-        <f>E17/D17</f>
-        <v/>
-      </c>
-      <c r="G17" s="46">
-        <f>'SOURCE 3 — HR Timesheet'!E17/'SOURCE 3 — HR Timesheet'!D17</f>
-        <v/>
+      <c r="E17" s="45" t="n">
+        <v>77000</v>
+      </c>
+      <c r="F17" s="46" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="G17" s="46" t="n">
+        <v>0.55</v>
       </c>
       <c r="H17" s="43" t="inlineStr">
         <is>
@@ -1612,17 +1570,14 @@
       <c r="D18" s="39" t="n">
         <v>330000</v>
       </c>
-      <c r="E18" s="39">
-        <f>'SOURCE 1 — SAP Finance'!G18</f>
-        <v/>
-      </c>
-      <c r="F18" s="40">
-        <f>E18/D18</f>
-        <v/>
-      </c>
-      <c r="G18" s="40">
-        <f>'SOURCE 3 — HR Timesheet'!E18/'SOURCE 3 — HR Timesheet'!D18</f>
-        <v/>
+      <c r="E18" s="39" t="n">
+        <v>118000</v>
+      </c>
+      <c r="F18" s="40" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="G18" s="40" t="n">
+        <v>0.6</v>
       </c>
       <c r="H18" s="37" t="inlineStr">
         <is>
@@ -1669,17 +1624,14 @@
       <c r="D19" s="45" t="n">
         <v>195000</v>
       </c>
-      <c r="E19" s="45">
-        <f>'SOURCE 1 — SAP Finance'!G19</f>
-        <v/>
-      </c>
-      <c r="F19" s="46">
-        <f>E19/D19</f>
-        <v/>
-      </c>
-      <c r="G19" s="46">
-        <f>'SOURCE 3 — HR Timesheet'!E19/'SOURCE 3 — HR Timesheet'!D19</f>
-        <v/>
+      <c r="E19" s="45" t="n">
+        <v>44000</v>
+      </c>
+      <c r="F19" s="46" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="G19" s="46" t="n">
+        <v>0.9399999999999999</v>
       </c>
       <c r="H19" s="43" t="inlineStr">
         <is>
@@ -1726,17 +1678,14 @@
       <c r="D20" s="39" t="n">
         <v>550000</v>
       </c>
-      <c r="E20" s="39">
-        <f>'SOURCE 1 — SAP Finance'!G20</f>
-        <v/>
-      </c>
-      <c r="F20" s="40">
-        <f>E20/D20</f>
-        <v/>
-      </c>
-      <c r="G20" s="40">
-        <f>'SOURCE 3 — HR Timesheet'!E20/'SOURCE 3 — HR Timesheet'!D20</f>
-        <v/>
+      <c r="E20" s="39" t="n">
+        <v>223000</v>
+      </c>
+      <c r="F20" s="40" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="G20" s="40" t="n">
+        <v>0.59</v>
       </c>
       <c r="H20" s="37" t="inlineStr">
         <is>
@@ -1783,17 +1732,14 @@
       <c r="D21" s="45" t="n">
         <v>125000</v>
       </c>
-      <c r="E21" s="45">
-        <f>'SOURCE 1 — SAP Finance'!G21</f>
-        <v/>
-      </c>
-      <c r="F21" s="46">
-        <f>E21/D21</f>
-        <v/>
-      </c>
-      <c r="G21" s="46">
-        <f>'SOURCE 3 — HR Timesheet'!E21/'SOURCE 3 — HR Timesheet'!D21</f>
-        <v/>
+      <c r="E21" s="45" t="n">
+        <v>121000</v>
+      </c>
+      <c r="F21" s="46" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="G21" s="46" t="n">
+        <v>0.57</v>
       </c>
       <c r="H21" s="43" t="inlineStr">
         <is>
@@ -1840,17 +1786,14 @@
       <c r="D22" s="39" t="n">
         <v>440000</v>
       </c>
-      <c r="E22" s="39">
-        <f>'SOURCE 1 — SAP Finance'!G22</f>
-        <v/>
-      </c>
-      <c r="F22" s="40">
-        <f>E22/D22</f>
-        <v/>
-      </c>
-      <c r="G22" s="40">
-        <f>'SOURCE 3 — HR Timesheet'!E22/'SOURCE 3 — HR Timesheet'!D22</f>
-        <v/>
+      <c r="E22" s="39" t="n">
+        <v>189000</v>
+      </c>
+      <c r="F22" s="40" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="G22" s="40" t="n">
+        <v>0.76</v>
       </c>
       <c r="H22" s="37" t="inlineStr">
         <is>
@@ -1897,17 +1840,14 @@
       <c r="D23" s="45" t="n">
         <v>285000</v>
       </c>
-      <c r="E23" s="45">
-        <f>'SOURCE 1 — SAP Finance'!G23</f>
-        <v/>
-      </c>
-      <c r="F23" s="46">
-        <f>E23/D23</f>
-        <v/>
-      </c>
-      <c r="G23" s="46">
-        <f>'SOURCE 3 — HR Timesheet'!E23/'SOURCE 3 — HR Timesheet'!D23</f>
-        <v/>
+      <c r="E23" s="45" t="n">
+        <v>68000</v>
+      </c>
+      <c r="F23" s="46" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G23" s="46" t="n">
+        <v>0.89</v>
       </c>
       <c r="H23" s="43" t="inlineStr">
         <is>
@@ -1954,17 +1894,14 @@
       <c r="D24" s="39" t="n">
         <v>175000</v>
       </c>
-      <c r="E24" s="39">
-        <f>'SOURCE 1 — SAP Finance'!G24</f>
-        <v/>
-      </c>
-      <c r="F24" s="40">
-        <f>E24/D24</f>
-        <v/>
-      </c>
-      <c r="G24" s="40">
-        <f>'SOURCE 3 — HR Timesheet'!E24/'SOURCE 3 — HR Timesheet'!D24</f>
-        <v/>
+      <c r="E24" s="39" t="n">
+        <v>168000</v>
+      </c>
+      <c r="F24" s="40" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G24" s="40" t="n">
+        <v>0.85</v>
       </c>
       <c r="H24" s="37" t="inlineStr">
         <is>
@@ -2011,17 +1948,14 @@
       <c r="D25" s="45" t="n">
         <v>490000</v>
       </c>
-      <c r="E25" s="45">
-        <f>'SOURCE 1 — SAP Finance'!G25</f>
-        <v/>
-      </c>
-      <c r="F25" s="46">
-        <f>E25/D25</f>
-        <v/>
-      </c>
-      <c r="G25" s="46">
-        <f>'SOURCE 3 — HR Timesheet'!E25/'SOURCE 3 — HR Timesheet'!D25</f>
-        <v/>
+      <c r="E25" s="45" t="n">
+        <v>201000</v>
+      </c>
+      <c r="F25" s="46" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="G25" s="46" t="n">
+        <v>0.79</v>
       </c>
       <c r="H25" s="43" t="inlineStr">
         <is>
@@ -2068,17 +2002,14 @@
       <c r="D26" s="39" t="n">
         <v>360000</v>
       </c>
-      <c r="E26" s="39">
-        <f>'SOURCE 1 — SAP Finance'!G26</f>
-        <v/>
-      </c>
-      <c r="F26" s="40">
-        <f>E26/D26</f>
-        <v/>
-      </c>
-      <c r="G26" s="40">
-        <f>'SOURCE 3 — HR Timesheet'!E26/'SOURCE 3 — HR Timesheet'!D26</f>
-        <v/>
+      <c r="E26" s="39" t="n">
+        <v>92000</v>
+      </c>
+      <c r="F26" s="40" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="G26" s="40" t="n">
+        <v>0.9399999999999999</v>
       </c>
       <c r="H26" s="37" t="inlineStr">
         <is>
@@ -2125,17 +2056,14 @@
       <c r="D27" s="45" t="n">
         <v>215000</v>
       </c>
-      <c r="E27" s="45">
-        <f>'SOURCE 1 — SAP Finance'!G27</f>
-        <v/>
-      </c>
-      <c r="F27" s="46">
-        <f>E27/D27</f>
-        <v/>
-      </c>
-      <c r="G27" s="46">
-        <f>'SOURCE 3 — HR Timesheet'!E27/'SOURCE 3 — HR Timesheet'!D27</f>
-        <v/>
+      <c r="E27" s="45" t="n">
+        <v>209000</v>
+      </c>
+      <c r="F27" s="46" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="G27" s="46" t="n">
+        <v>0.89</v>
       </c>
       <c r="H27" s="43" t="inlineStr">
         <is>
@@ -2182,17 +2110,14 @@
       <c r="D28" s="39" t="n">
         <v>520000</v>
       </c>
-      <c r="E28" s="39">
-        <f>'SOURCE 1 — SAP Finance'!G28</f>
-        <v/>
-      </c>
-      <c r="F28" s="40">
-        <f>E28/D28</f>
-        <v/>
-      </c>
-      <c r="G28" s="40">
-        <f>'SOURCE 3 — HR Timesheet'!E28/'SOURCE 3 — HR Timesheet'!D28</f>
-        <v/>
+      <c r="E28" s="39" t="n">
+        <v>145000</v>
+      </c>
+      <c r="F28" s="40" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="G28" s="40" t="n">
+        <v>0.7</v>
       </c>
       <c r="H28" s="37" t="inlineStr">
         <is>
@@ -2233,14 +2158,16 @@
         <v/>
       </c>
       <c r="E29" s="52">
-        <f>SUM(E4:E28)</f>
+        <f>'SOURCE 1 — SAP Finance'!G29</f>
         <v/>
       </c>
       <c r="F29" s="53">
         <f>E29/D29</f>
         <v/>
       </c>
-      <c r="G29" s="54" t="n"/>
+      <c r="G29" s="54" t="n">
+        <v>0.73</v>
+      </c>
       <c r="H29" s="54" t="n"/>
       <c r="I29" s="54" t="n"/>
       <c r="J29" s="54" t="n"/>
@@ -3335,7 +3262,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="B29" t="n">
+      <c r="B29" s="32" t="n">
         <v>372507</v>
       </c>
     </row>
@@ -5310,11 +5237,15 @@
       </c>
     </row>
     <row r="29">
-      <c r="D29" t="n">
+      <c r="D29" s="32" t="n">
         <v>960</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E29" s="32" t="n">
         <v>703</v>
+      </c>
+      <c r="G29" s="32">
+        <f>E29/D29</f>
+        <v/>
       </c>
     </row>
   </sheetData>
